--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/tienda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9097ED8F-7675-4613-A4AB-77C96E4CDC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69EF108A-ED3E-45D6-ADFF-F02DA34B0CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{32C1DDBA-4E73-42D9-B240-A571054BC618}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{24072905-EB78-43FF-AB26-A0FE06EC2951}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5407,7 +5407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4546F660-4CDB-4B73-8BEE-1291937D2295}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A868D1B-9F87-49A2-AF21-6C610B2BE067}">
   <dimension ref="A1:N913"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -5695,7 +5695,7 @@
         <v>297</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -6395,7 +6395,7 @@
         <v>4750</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -6896,7 +6896,7 @@
         <v>7000</v>
       </c>
       <c r="L36">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -6937,7 +6937,7 @@
         <v>7000</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>5090</v>
       </c>
       <c r="L47">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -7670,7 +7670,7 @@
         <v>3169</v>
       </c>
       <c r="L54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -8010,13 +8010,13 @@
         <v>12000</v>
       </c>
       <c r="J62">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="K62">
         <v>2897</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -8060,7 +8060,7 @@
         <v>2897</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -8089,7 +8089,7 @@
         <v>2897</v>
       </c>
       <c r="G64">
-        <v>9918.5</v>
+        <v>12000</v>
       </c>
       <c r="H64">
         <v>21</v>
@@ -8532,7 +8532,7 @@
         <v>711</v>
       </c>
       <c r="L74">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -9528,10 +9528,10 @@
         <v>21</v>
       </c>
       <c r="I98">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="J98">
-        <v>4000</v>
+        <v>6500</v>
       </c>
       <c r="K98">
         <v>4000</v>
@@ -9619,7 +9619,7 @@
         <v>4000</v>
       </c>
       <c r="L100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>18000</v>
       </c>
       <c r="L122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122">
         <v>0</v>
@@ -10689,7 +10689,7 @@
         <v>18000</v>
       </c>
       <c r="L125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M125">
         <v>0</v>
@@ -11170,7 +11170,7 @@
         <v>18000</v>
       </c>
       <c r="L136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M136">
         <v>0</v>
@@ -11337,7 +11337,7 @@
         <v>18000</v>
       </c>
       <c r="L140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140">
         <v>0</v>
@@ -11445,25 +11445,25 @@
         <v>178</v>
       </c>
       <c r="F143">
-        <v>5412</v>
+        <v>6193</v>
       </c>
       <c r="G143">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="H143">
         <v>21</v>
       </c>
       <c r="I143">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="J143">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="K143">
-        <v>10000</v>
+        <v>6193</v>
       </c>
       <c r="L143">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M143">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>1389</v>
       </c>
       <c r="L146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -11636,7 +11636,7 @@
         <v>20872</v>
       </c>
       <c r="L147">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M147">
         <v>0</v>
@@ -12550,7 +12550,7 @@
         <v>1600</v>
       </c>
       <c r="L169">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M169">
         <v>0</v>
@@ -12594,7 +12594,7 @@
         <v>2200</v>
       </c>
       <c r="L170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M170">
         <v>0</v>
@@ -13458,7 +13458,7 @@
         <v>92</v>
       </c>
       <c r="L191">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M191">
         <v>0</v>
@@ -13886,7 +13886,7 @@
         <v>689</v>
       </c>
       <c r="L201">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="M201">
         <v>0</v>
@@ -14815,7 +14815,7 @@
         <v>12022</v>
       </c>
       <c r="L223">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M223">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>9000</v>
       </c>
       <c r="L237">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M237">
         <v>0</v>
@@ -16888,7 +16888,7 @@
         <v>8884</v>
       </c>
       <c r="L271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M271">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>1215.2</v>
       </c>
       <c r="L280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M280">
         <v>0</v>
@@ -17746,16 +17746,16 @@
         <v>2700</v>
       </c>
       <c r="G292">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H292">
         <v>21</v>
       </c>
       <c r="I292">
-        <v>2700</v>
+        <v>12000</v>
       </c>
       <c r="J292">
-        <v>2700</v>
+        <v>5000</v>
       </c>
       <c r="K292">
         <v>2700</v>
@@ -17843,7 +17843,7 @@
         <v>1900</v>
       </c>
       <c r="L294">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M294">
         <v>0</v>
@@ -17925,7 +17925,7 @@
         <v>2359</v>
       </c>
       <c r="L296">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M296">
         <v>0</v>
@@ -18388,7 +18388,7 @@
         <v>3225.8</v>
       </c>
       <c r="L307">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="M307">
         <v>0</v>
@@ -18496,16 +18496,16 @@
         <v>4500</v>
       </c>
       <c r="G310">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H310">
         <v>21</v>
       </c>
       <c r="I310">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="J310">
-        <v>4500</v>
+        <v>7500</v>
       </c>
       <c r="K310">
         <v>4500</v>
@@ -18540,7 +18540,7 @@
         <v>2850</v>
       </c>
       <c r="G311">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H311">
         <v>21</v>
@@ -18549,13 +18549,13 @@
         <v>10000</v>
       </c>
       <c r="J311">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K311">
         <v>2850</v>
       </c>
       <c r="L311">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M311">
         <v>0</v>
@@ -19211,7 +19211,7 @@
         <v>15000</v>
       </c>
       <c r="L327">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M327">
         <v>0</v>
@@ -20318,7 +20318,7 @@
         <v>5342</v>
       </c>
       <c r="L354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M354">
         <v>0</v>
@@ -20687,7 +20687,7 @@
         <v>950</v>
       </c>
       <c r="L363">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M363">
         <v>0</v>
@@ -20974,7 +20974,7 @@
         <v>0</v>
       </c>
       <c r="L370">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M370">
         <v>0</v>
@@ -21094,13 +21094,13 @@
         <v>15000</v>
       </c>
       <c r="J373">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="K373">
         <v>2400</v>
       </c>
       <c r="L373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M373">
         <v>0</v>
@@ -21311,7 +21311,7 @@
         <v>3169</v>
       </c>
       <c r="L378">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -21516,7 +21516,7 @@
         <v>2000</v>
       </c>
       <c r="L383">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M383">
         <v>0</v>
@@ -22005,7 +22005,7 @@
         <v>885</v>
       </c>
       <c r="L395">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M395">
         <v>0</v>
@@ -22046,7 +22046,7 @@
         <v>2070</v>
       </c>
       <c r="L396">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M396">
         <v>0</v>
@@ -22383,7 +22383,7 @@
         <v>33500</v>
       </c>
       <c r="L404">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M404">
         <v>0</v>
@@ -23968,7 +23968,7 @@
         <v>5262</v>
       </c>
       <c r="L442">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -24534,7 +24534,7 @@
         <v>12261</v>
       </c>
       <c r="L455">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M455">
         <v>0</v>
@@ -24704,7 +24704,7 @@
         <v>23000</v>
       </c>
       <c r="L459">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M459">
         <v>0</v>
@@ -24748,7 +24748,7 @@
         <v>21000</v>
       </c>
       <c r="L460">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M460">
         <v>0</v>
@@ -24877,7 +24877,7 @@
         <v>20000</v>
       </c>
       <c r="L463">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M463">
         <v>0</v>
@@ -24965,7 +24965,7 @@
         <v>22000</v>
       </c>
       <c r="L465">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M465">
         <v>0</v>
@@ -25053,7 +25053,7 @@
         <v>22000</v>
       </c>
       <c r="L467">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M467">
         <v>0</v>
@@ -25469,7 +25469,7 @@
         <v>20000</v>
       </c>
       <c r="L477">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M477">
         <v>0</v>
@@ -25492,25 +25492,25 @@
         <v>28</v>
       </c>
       <c r="F478">
-        <v>15750</v>
+        <v>15549</v>
       </c>
       <c r="G478">
-        <v>58000</v>
+        <v>55000</v>
       </c>
       <c r="H478">
         <v>21</v>
       </c>
       <c r="I478">
-        <v>58000</v>
+        <v>55000</v>
       </c>
       <c r="J478">
         <v>26000</v>
       </c>
       <c r="K478">
-        <v>26000</v>
+        <v>15549</v>
       </c>
       <c r="L478">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M478">
         <v>0</v>
@@ -25580,7 +25580,7 @@
         <v>202</v>
       </c>
       <c r="F480">
-        <v>11641</v>
+        <v>12031</v>
       </c>
       <c r="G480">
         <v>40000</v>
@@ -25598,7 +25598,7 @@
         <v>20000</v>
       </c>
       <c r="L480">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M480">
         <v>0</v>
@@ -25668,7 +25668,7 @@
         <v>202</v>
       </c>
       <c r="F482">
-        <v>13193</v>
+        <v>13008</v>
       </c>
       <c r="G482">
         <v>45000</v>
@@ -25683,10 +25683,10 @@
         <v>23000</v>
       </c>
       <c r="K482">
-        <v>23000</v>
+        <v>13008</v>
       </c>
       <c r="L482">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M482">
         <v>0</v>
@@ -25800,7 +25800,7 @@
         <v>264</v>
       </c>
       <c r="F485">
-        <v>11710</v>
+        <v>11702</v>
       </c>
       <c r="G485">
         <v>40000</v>
@@ -25815,10 +25815,10 @@
         <v>20000</v>
       </c>
       <c r="K485">
-        <v>20000</v>
+        <v>11702</v>
       </c>
       <c r="L485">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -25906,7 +25906,7 @@
         <v>23000</v>
       </c>
       <c r="L487">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M487">
         <v>0</v>
@@ -25950,7 +25950,7 @@
         <v>22000</v>
       </c>
       <c r="L488">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -25994,7 +25994,7 @@
         <v>25000</v>
       </c>
       <c r="L489">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M489">
         <v>0</v>
@@ -26099,7 +26099,7 @@
         <v>816</v>
       </c>
       <c r="F492">
-        <v>16000</v>
+        <v>15958</v>
       </c>
       <c r="G492">
         <v>55000</v>
@@ -26114,10 +26114,10 @@
         <v>30000</v>
       </c>
       <c r="K492">
-        <v>30000</v>
+        <v>15958</v>
       </c>
       <c r="L492">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M492">
         <v>0</v>
@@ -26161,7 +26161,7 @@
         <v>23000</v>
       </c>
       <c r="L493">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M493">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         <v>25000</v>
       </c>
       <c r="L494">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M494">
         <v>0</v>
@@ -26243,7 +26243,7 @@
         <v>25000</v>
       </c>
       <c r="L495">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M495">
         <v>0</v>
@@ -26372,7 +26372,7 @@
         <v>23000</v>
       </c>
       <c r="L498">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M498">
         <v>0</v>
@@ -26498,7 +26498,7 @@
         <v>20000</v>
       </c>
       <c r="L501">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M501">
         <v>0</v>
@@ -26829,7 +26829,7 @@
         <v>20000</v>
       </c>
       <c r="L509">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M509">
         <v>0</v>
@@ -26873,7 +26873,7 @@
         <v>21000</v>
       </c>
       <c r="L510">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M510">
         <v>0</v>
@@ -26914,7 +26914,7 @@
         <v>25000</v>
       </c>
       <c r="L511">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M511">
         <v>0</v>
@@ -26999,7 +26999,7 @@
         <v>20000</v>
       </c>
       <c r="L513">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M513">
         <v>0</v>
@@ -27345,7 +27345,7 @@
         <v>20000</v>
       </c>
       <c r="L521">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M521">
         <v>0</v>
@@ -27412,7 +27412,7 @@
         <v>264</v>
       </c>
       <c r="F523">
-        <v>11460</v>
+        <v>11435</v>
       </c>
       <c r="G523">
         <v>40000</v>
@@ -27427,10 +27427,10 @@
         <v>20000</v>
       </c>
       <c r="K523">
-        <v>20000</v>
+        <v>11435</v>
       </c>
       <c r="L523">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M523">
         <v>0</v>
@@ -27500,7 +27500,7 @@
         <v>264</v>
       </c>
       <c r="F525">
-        <v>11173</v>
+        <v>11159</v>
       </c>
       <c r="G525">
         <v>40000</v>
@@ -27515,10 +27515,10 @@
         <v>18000</v>
       </c>
       <c r="K525">
-        <v>18000</v>
+        <v>11159</v>
       </c>
       <c r="L525">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M525">
         <v>0</v>
@@ -27562,7 +27562,7 @@
         <v>15103</v>
       </c>
       <c r="L526">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M526">
         <v>0</v>
@@ -27732,7 +27732,7 @@
         <v>20000</v>
       </c>
       <c r="L530">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M530">
         <v>0</v>
@@ -27993,7 +27993,7 @@
         <v>23000</v>
       </c>
       <c r="L536">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M536">
         <v>0</v>
@@ -28063,7 +28063,7 @@
         <v>264</v>
       </c>
       <c r="F538">
-        <v>12420</v>
+        <v>12298</v>
       </c>
       <c r="G538">
         <v>45000</v>
@@ -28078,10 +28078,10 @@
         <v>22000</v>
       </c>
       <c r="K538">
-        <v>22000</v>
+        <v>12298</v>
       </c>
       <c r="L538">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M538">
         <v>0</v>
@@ -28169,7 +28169,7 @@
         <v>23000</v>
       </c>
       <c r="L540">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>178</v>
       </c>
       <c r="F541">
-        <v>9940</v>
+        <v>11239</v>
       </c>
       <c r="G541">
         <v>40000</v>
@@ -28204,16 +28204,16 @@
         <v>21</v>
       </c>
       <c r="I541">
-        <v>39760</v>
+        <v>40000</v>
       </c>
       <c r="J541">
         <v>20000</v>
       </c>
       <c r="K541">
-        <v>20000</v>
+        <v>11239</v>
       </c>
       <c r="L541">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M541">
         <v>0</v>
@@ -28389,7 +28389,7 @@
         <v>21000</v>
       </c>
       <c r="L545">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M545">
         <v>0</v>
@@ -28641,7 +28641,7 @@
         <v>22000</v>
       </c>
       <c r="L551">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M551">
         <v>0</v>
@@ -28685,7 +28685,7 @@
         <v>30000</v>
       </c>
       <c r="L552">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M552">
         <v>0</v>
@@ -28817,7 +28817,7 @@
         <v>30000</v>
       </c>
       <c r="L555">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M555">
         <v>0</v>
@@ -29145,25 +29145,25 @@
         <v>178</v>
       </c>
       <c r="F563">
-        <v>13492</v>
+        <v>12995</v>
       </c>
       <c r="G563">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="H563">
         <v>21</v>
       </c>
       <c r="I563">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="J563">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="K563">
-        <v>23000</v>
+        <v>12995</v>
       </c>
       <c r="L563">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M563">
         <v>0</v>
@@ -29204,7 +29204,7 @@
         <v>25000</v>
       </c>
       <c r="L564">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M564">
         <v>0</v>
@@ -29274,7 +29274,7 @@
         <v>264</v>
       </c>
       <c r="F566">
-        <v>12428</v>
+        <v>12328</v>
       </c>
       <c r="G566">
         <v>45000</v>
@@ -29286,13 +29286,13 @@
         <v>45000</v>
       </c>
       <c r="J566">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K566">
-        <v>22000</v>
+        <v>12328</v>
       </c>
       <c r="L566">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M566">
         <v>0</v>
@@ -29318,7 +29318,7 @@
         <v>264</v>
       </c>
       <c r="F567">
-        <v>12470</v>
+        <v>12395</v>
       </c>
       <c r="G567">
         <v>45000</v>
@@ -29336,7 +29336,7 @@
         <v>22000</v>
       </c>
       <c r="L567">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M567">
         <v>0</v>
@@ -29597,7 +29597,7 @@
         <v>30000</v>
       </c>
       <c r="L573">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M573">
         <v>0</v>
@@ -29685,7 +29685,7 @@
         <v>30000</v>
       </c>
       <c r="L575">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M575">
         <v>0</v>
@@ -30069,7 +30069,7 @@
         <v>18000</v>
       </c>
       <c r="L584">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M584">
         <v>0</v>
@@ -30113,7 +30113,7 @@
         <v>20000</v>
       </c>
       <c r="L585">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M585">
         <v>0</v>
@@ -30435,7 +30435,7 @@
         <v>1118</v>
       </c>
       <c r="F593">
-        <v>13600</v>
+        <v>15000</v>
       </c>
       <c r="G593">
         <v>48000</v>
@@ -30453,7 +30453,7 @@
         <v>24000</v>
       </c>
       <c r="L593">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M593">
         <v>0</v>
@@ -30479,7 +30479,7 @@
         <v>1118</v>
       </c>
       <c r="F594">
-        <v>13050</v>
+        <v>13440</v>
       </c>
       <c r="G594">
         <v>45000</v>
@@ -30494,10 +30494,10 @@
         <v>23000</v>
       </c>
       <c r="K594">
-        <v>23000</v>
+        <v>13440</v>
       </c>
       <c r="L594">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M594">
         <v>0</v>
@@ -30567,7 +30567,7 @@
         <v>1118</v>
       </c>
       <c r="F596">
-        <v>13600</v>
+        <v>13680</v>
       </c>
       <c r="G596">
         <v>48000</v>
@@ -30582,10 +30582,10 @@
         <v>23000</v>
       </c>
       <c r="K596">
-        <v>23000</v>
+        <v>13680</v>
       </c>
       <c r="L596">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M596">
         <v>0</v>
@@ -30629,7 +30629,7 @@
         <v>26000</v>
       </c>
       <c r="L597">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M597">
         <v>0</v>
@@ -30655,7 +30655,7 @@
         <v>1118</v>
       </c>
       <c r="F598">
-        <v>16000</v>
+        <v>16090</v>
       </c>
       <c r="G598">
         <v>48000</v>
@@ -30667,10 +30667,10 @@
         <v>48000</v>
       </c>
       <c r="J598">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="K598">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="L598">
         <v>3</v>
@@ -30928,7 +30928,7 @@
         <v>25000</v>
       </c>
       <c r="L604">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M604">
         <v>0</v>
@@ -30969,7 +30969,7 @@
         <v>22000</v>
       </c>
       <c r="L605">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M605">
         <v>0</v>
@@ -31054,7 +31054,7 @@
         <v>24000</v>
       </c>
       <c r="L607">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M607">
         <v>0</v>
@@ -31186,7 +31186,7 @@
         <v>21000</v>
       </c>
       <c r="L610">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M610">
         <v>0</v>
@@ -31763,7 +31763,7 @@
         <v>264</v>
       </c>
       <c r="F624">
-        <v>12276</v>
+        <v>12199</v>
       </c>
       <c r="G624">
         <v>45000</v>
@@ -31778,10 +31778,10 @@
         <v>21000</v>
       </c>
       <c r="K624">
-        <v>21000</v>
+        <v>12199</v>
       </c>
       <c r="L624">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M624">
         <v>0</v>
@@ -33068,7 +33068,7 @@
         <v>3806</v>
       </c>
       <c r="L654">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M654">
         <v>0</v>
@@ -33824,7 +33824,7 @@
         <v>9000</v>
       </c>
       <c r="L672">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M672">
         <v>0</v>
@@ -33865,7 +33865,7 @@
         <v>8000</v>
       </c>
       <c r="L673">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M673">
         <v>0</v>
@@ -33909,7 +33909,7 @@
         <v>4718</v>
       </c>
       <c r="L674">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M674">
         <v>0</v>
@@ -33950,7 +33950,7 @@
         <v>3720</v>
       </c>
       <c r="L675">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M675">
         <v>0</v>
@@ -34709,7 +34709,7 @@
         <v>112</v>
       </c>
       <c r="L693">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M693">
         <v>0</v>
@@ -35614,7 +35614,7 @@
         <v>10000</v>
       </c>
       <c r="L715">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M715">
         <v>0</v>
@@ -36975,7 +36975,7 @@
         <v>10000</v>
       </c>
       <c r="L746">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M746">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>10000</v>
       </c>
       <c r="L808">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M808">
         <v>0</v>
@@ -40340,7 +40340,7 @@
         <v>4528</v>
       </c>
       <c r="L825">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M825">
         <v>0</v>
@@ -40513,7 +40513,7 @@
         <v>10795</v>
       </c>
       <c r="L829">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M829">
         <v>0</v>
@@ -40548,13 +40548,13 @@
         <v>18000</v>
       </c>
       <c r="J830">
-        <v>18000</v>
+        <v>9500</v>
       </c>
       <c r="K830">
         <v>5344</v>
       </c>
       <c r="L830">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M830">
         <v>0</v>
@@ -40595,7 +40595,7 @@
         <v>2328</v>
       </c>
       <c r="L831">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M831">
         <v>0</v>
@@ -41301,7 +41301,7 @@
         <v>2435</v>
       </c>
       <c r="L848">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M848">
         <v>0</v>
@@ -41805,7 +41805,7 @@
         <v>1000</v>
       </c>
       <c r="L860">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="M860">
         <v>0</v>
@@ -42051,7 +42051,7 @@
         <v>1150</v>
       </c>
       <c r="L866">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M866">
         <v>0</v>
@@ -43466,7 +43466,7 @@
         <v>2264</v>
       </c>
       <c r="L900">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M900">
         <v>0</v>
@@ -43677,7 +43677,7 @@
         <v>500</v>
       </c>
       <c r="L905">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M905">
         <v>0</v>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9af133bd758b7a26/Documentos/novacenter/datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documentos\novacenter\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69EF108A-ED3E-45D6-ADFF-F02DA34B0CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E2F766-C778-424A-9EF5-E252725F88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{24072905-EB78-43FF-AB26-A0FE06EC2951}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{24072905-EB78-43FF-AB26-A0FE06EC2951}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20605,7 +20605,7 @@
         <v>1250</v>
       </c>
       <c r="L361">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M361">
         <v>0</v>
